--- a/Excel/PetTraitConfig.xlsx
+++ b/Excel/PetTraitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="固定特性" sheetId="2" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="104">
   <si>
     <t>#</t>
   </si>
@@ -129,6 +129,9 @@
     <t>AtrVueList1</t>
   </si>
   <si>
+    <t>RiseType</t>
+  </si>
+  <si>
     <t>StartQuality</t>
   </si>
   <si>
@@ -279,6 +282,9 @@
     <t>20,10</t>
   </si>
   <si>
+    <t>1,1</t>
+  </si>
+  <si>
     <t>生命加成+10%，生命增幅+5%</t>
   </si>
   <si>
@@ -306,43 +312,46 @@
     <t>11,12</t>
   </si>
   <si>
+    <t>5,5</t>
+  </si>
+  <si>
     <t>10,10</t>
   </si>
   <si>
+    <t>攻击速度+10%，移动速度+10%</t>
+  </si>
+  <si>
+    <t>子弹时间</t>
+  </si>
+  <si>
+    <t>10,22</t>
+  </si>
+  <si>
+    <t>5,25</t>
+  </si>
+  <si>
+    <t>10,50</t>
+  </si>
+  <si>
+    <t>技能冷却+10%，暴击伤害+50%</t>
+  </si>
+  <si>
+    <t>射手直觉</t>
+  </si>
+  <si>
+    <t>13,14</t>
+  </si>
+  <si>
+    <t>命中+10%，闪避+10%</t>
+  </si>
+  <si>
+    <t>真男人</t>
+  </si>
+  <si>
+    <t>10001,10002</t>
+  </si>
+  <si>
     <t>20,20</t>
-  </si>
-  <si>
-    <t>攻击速度+10%，移动速度+10%</t>
-  </si>
-  <si>
-    <t>子弹时间</t>
-  </si>
-  <si>
-    <t>10,22</t>
-  </si>
-  <si>
-    <t>10,50</t>
-  </si>
-  <si>
-    <t>20,100</t>
-  </si>
-  <si>
-    <t>技能冷却+10%，暴击伤害+50%</t>
-  </si>
-  <si>
-    <t>射手直觉</t>
-  </si>
-  <si>
-    <t>13,14</t>
-  </si>
-  <si>
-    <t>命中+10%，闪避+10%</t>
-  </si>
-  <si>
-    <t>真男人</t>
-  </si>
-  <si>
-    <t>10001,10002</t>
   </si>
   <si>
     <t>防御倍率+10%，生命倍率+10%</t>
@@ -1384,29 +1393,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O105"/>
+  <dimension ref="C1:P105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="12.8333333333333" style="1" customWidth="1"/>
     <col min="5" max="9" width="13" style="1" customWidth="1"/>
     <col min="10" max="10" width="17" style="1" customWidth="1"/>
-    <col min="11" max="14" width="9" style="1"/>
-    <col min="15" max="15" width="14.1666666666667" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="11" max="11" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="12" max="13" width="11.5833333333333" style="1" customWidth="1"/>
+    <col min="14" max="15" width="9" style="1"/>
+    <col min="16" max="16" width="14.1666666666667" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:15">
-      <c r="O1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:15">
-      <c r="O2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="1" customHeight="1" spans="3:16">
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:16">
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1446,10 +1457,13 @@
       <c r="O3" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -1487,49 +1501,55 @@
       <c r="O4" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1537,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1">
         <v>100</v>
@@ -1555,23 +1575,26 @@
         <v>1</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6" s="1">
         <f t="shared" ref="L6:L19" si="0">K6*2</f>
         <v>4000</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" s="1">
         <v>0</v>
       </c>
-      <c r="O6" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1579,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1">
         <v>100</v>
@@ -1597,23 +1620,26 @@
         <v>2</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
       <c r="M7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N7" s="1">
         <v>0</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1621,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1">
         <v>100</v>
@@ -1639,23 +1665,26 @@
         <v>3</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L8" s="1">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
       <c r="M8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N8" s="1">
         <v>0</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1663,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="1">
         <v>100</v>
@@ -1681,23 +1710,26 @@
         <v>4</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" s="1">
         <v>0</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1705,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1">
         <v>100</v>
@@ -1723,23 +1755,26 @@
         <v>5</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L10" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" s="1">
         <v>0</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1747,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1">
         <v>100</v>
@@ -1765,23 +1800,26 @@
         <v>6</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="M11" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" s="1">
         <v>0</v>
       </c>
-      <c r="O11" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C12" s="1">
         <v>10</v>
       </c>
@@ -1789,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="1">
         <v>100</v>
@@ -1810,20 +1848,23 @@
         <v>5</v>
       </c>
       <c r="L12" s="1">
-        <f>K12*2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="M12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="1">
         <v>0</v>
       </c>
-      <c r="O12" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C13" s="1">
         <v>11</v>
       </c>
@@ -1831,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1">
         <v>100</v>
@@ -1852,20 +1893,23 @@
         <v>5</v>
       </c>
       <c r="L13" s="1">
-        <f>K13*2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="M13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="1">
         <v>0</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:15">
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:16">
       <c r="C14" s="1">
         <v>12</v>
       </c>
@@ -1873,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" s="1">
         <v>100</v>
@@ -1894,20 +1938,23 @@
         <v>5</v>
       </c>
       <c r="L14" s="1">
-        <f>K14*2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="M14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="1">
         <v>0</v>
       </c>
-      <c r="O14" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C15" s="1">
         <v>13</v>
       </c>
@@ -1915,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" s="1">
         <v>100</v>
@@ -1936,20 +1983,23 @@
         <v>5</v>
       </c>
       <c r="L15" s="1">
-        <f>K15*2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="M15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="1">
         <v>0</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C16" s="1">
         <v>14</v>
       </c>
@@ -1957,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -1978,20 +2028,23 @@
         <v>5</v>
       </c>
       <c r="L16" s="1">
-        <f>K16*2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="M16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="1">
         <v>0</v>
       </c>
-      <c r="O16" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C17" s="1">
         <v>22</v>
       </c>
@@ -1999,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" s="1">
         <v>100</v>
@@ -2020,26 +2073,29 @@
         <v>20</v>
       </c>
       <c r="L17" s="1">
-        <f>K17*2</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="M17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="1">
         <v>0</v>
       </c>
-      <c r="O17" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D18" s="3"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D19" s="3"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C20" s="1">
         <v>81</v>
       </c>
@@ -2047,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F20" s="1">
         <v>100</v>
@@ -2072,16 +2128,19 @@
         <v>10</v>
       </c>
       <c r="M20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="1">
         <v>0</v>
       </c>
-      <c r="O20" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C21" s="1">
         <v>82</v>
       </c>
@@ -2089,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" s="1">
         <v>100</v>
@@ -2114,16 +2173,19 @@
         <v>10</v>
       </c>
       <c r="M21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="1">
         <v>0</v>
       </c>
-      <c r="O21" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C22" s="1">
         <v>83</v>
       </c>
@@ -2131,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F22" s="1">
         <v>100</v>
@@ -2156,16 +2218,19 @@
         <v>6</v>
       </c>
       <c r="M22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="1">
         <v>0</v>
       </c>
-      <c r="O22" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C23" s="1">
         <v>84</v>
       </c>
@@ -2173,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F23" s="1">
         <v>100</v>
@@ -2198,16 +2263,19 @@
         <v>6</v>
       </c>
       <c r="M23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="1">
         <v>0</v>
       </c>
-      <c r="O23" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C24" s="1">
         <v>85</v>
       </c>
@@ -2215,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F24" s="1">
         <v>100</v>
@@ -2240,16 +2308,19 @@
         <v>20</v>
       </c>
       <c r="M24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="1">
         <v>0</v>
       </c>
-      <c r="O24" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O24" s="1">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C25" s="1">
         <v>86</v>
       </c>
@@ -2257,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F25" s="1">
         <v>100</v>
@@ -2282,34 +2353,37 @@
         <v>20</v>
       </c>
       <c r="M25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="1">
         <v>0</v>
       </c>
-      <c r="O25" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O25" s="1">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D26" s="5"/>
     </row>
-    <row r="27" customHeight="1" spans="3:15">
+    <row r="27" customHeight="1" spans="3:16">
       <c r="D27" s="4"/>
     </row>
-    <row r="28" customHeight="1" spans="3:15">
+    <row r="28" customHeight="1" spans="3:16">
       <c r="D28" s="3"/>
     </row>
-    <row r="29" customHeight="1" spans="3:15">
+    <row r="29" customHeight="1" spans="3:16">
       <c r="D29" s="3"/>
     </row>
-    <row r="30" customHeight="1" spans="3:15">
+    <row r="30" customHeight="1" spans="3:16">
       <c r="D30" s="6"/>
     </row>
-    <row r="31" customHeight="1" spans="3:15">
+    <row r="31" customHeight="1" spans="3:16">
       <c r="D31" s="3"/>
     </row>
-    <row r="32" customHeight="1" spans="3:15">
+    <row r="32" customHeight="1" spans="3:16">
       <c r="D32" s="6"/>
     </row>
     <row r="33" customHeight="1" spans="4:4">
@@ -2449,23 +2523,19 @@
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
     </row>
-    <row r="104" customHeight="1" spans="5:15">
+    <row r="104" customHeight="1" spans="5:16">
       <c r="E104" s="7"/>
       <c r="F104" s="7"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
-      <c r="O104" s="7"/>
-    </row>
-    <row r="105" customHeight="1" spans="5:15">
+      <c r="P104" s="7"/>
+    </row>
+    <row r="105" customHeight="1" spans="5:16">
       <c r="E105" s="7"/>
       <c r="F105" s="7"/>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
-      <c r="O105" s="7"/>
+      <c r="P105" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E3 F3 G3 H3 O3 C4:E4 F4 G4 H4 O4 C5:E5 F5 G5 H5 O5 M3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:N5 P3:P5 C3:H5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2478,8 +2548,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O85"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <dimension ref="C1:P55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="12.8333333333333" style="1" customWidth="1"/>
@@ -2487,23 +2557,23 @@
     <col min="10" max="10" width="17" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.1666666666667" style="1" customWidth="1"/>
     <col min="12" max="12" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.8333333333333" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9" style="1"/>
-    <col min="15" max="15" width="23.5833333333333" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="13" max="14" width="13.8333333333333" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9" style="1"/>
+    <col min="16" max="16" width="23.5833333333333" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:15">
-      <c r="O1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:15">
-      <c r="O2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="1" customHeight="1" spans="3:16">
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:16">
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2543,10 +2613,13 @@
       <c r="O3" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -2584,49 +2657,55 @@
       <c r="O4" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -2634,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F6" s="1">
         <v>6</v>
@@ -2649,25 +2728,28 @@
         <v>100</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="M6" s="1">
+        <v>61</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N6" s="1">
         <v>1</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>99</v>
       </c>
-      <c r="O6" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P6" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2675,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F7" s="1">
         <v>6</v>
@@ -2690,25 +2772,28 @@
         <v>100</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="M7" s="1">
+        <v>61</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N7" s="1">
         <v>1</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <v>99</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P7" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -2716,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F8" s="1">
         <v>6</v>
@@ -2731,25 +2816,28 @@
         <v>100</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="M8" s="1">
+        <v>61</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N8" s="1">
         <v>1</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>99</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P8" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -2757,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F9" s="1">
         <v>48</v>
@@ -2772,25 +2860,28 @@
         <v>30</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M9" s="1">
+        <v>73</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N9" s="1">
         <v>5</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>99</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P9" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -2798,7 +2889,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F10" s="1">
         <v>48</v>
@@ -2813,25 +2904,28 @@
         <v>30</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="M10" s="1">
+        <v>78</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N10" s="1">
         <v>5</v>
       </c>
-      <c r="N10" s="1">
+      <c r="O10" s="1">
         <v>99</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P10" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -2839,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F11" s="1">
         <v>36</v>
@@ -2854,25 +2948,28 @@
         <v>30</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M11" s="1">
+        <v>73</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" s="1">
         <v>5</v>
       </c>
-      <c r="N11" s="1">
+      <c r="O11" s="1">
         <v>99</v>
       </c>
-      <c r="O11" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P11" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -2880,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F12" s="1">
         <v>24</v>
@@ -2895,25 +2992,28 @@
         <v>50</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M12" s="1">
+        <v>85</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N12" s="1">
         <v>4</v>
       </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
         <v>99</v>
       </c>
-      <c r="O12" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P12" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
@@ -2921,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F13" s="1">
         <v>24</v>
@@ -2936,25 +3036,28 @@
         <v>50</v>
       </c>
       <c r="J13" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M13" s="1">
+      <c r="M13" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13" s="1">
         <v>4</v>
       </c>
-      <c r="N13" s="1">
+      <c r="O13" s="1">
         <v>99</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P13" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
@@ -2962,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F14" s="1">
         <v>24</v>
@@ -2974,34 +3077,39 @@
         <v>999</v>
       </c>
       <c r="I14" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M14" s="1">
+        <v>85</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N14" s="1">
         <v>4</v>
       </c>
-      <c r="N14" s="1">
+      <c r="O14" s="1">
         <v>99</v>
       </c>
-      <c r="O14" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P14" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
       <c r="E15" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F15" s="1">
         <v>24</v>
@@ -3013,34 +3121,39 @@
         <v>999</v>
       </c>
       <c r="I15" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M15" s="1">
+        <v>85</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N15" s="1">
         <v>1</v>
       </c>
-      <c r="N15" s="1">
+      <c r="O15" s="1">
         <v>99</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P15" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
       <c r="E16" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F16" s="1">
         <v>24</v>
@@ -3052,34 +3165,39 @@
         <v>999</v>
       </c>
       <c r="I16" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M16" s="1">
+        <v>85</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N16" s="1">
         <v>1</v>
       </c>
-      <c r="N16" s="1">
+      <c r="O16" s="1">
         <v>99</v>
       </c>
-      <c r="O16" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P16" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C17" s="1">
         <v>1012</v>
       </c>
-      <c r="D17" s="1"/>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
       <c r="E17" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F17" s="1">
         <v>24</v>
@@ -3094,67 +3212,70 @@
         <v>10</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L17" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1</v>
+      </c>
+      <c r="O17" s="1">
         <v>99</v>
       </c>
-      <c r="M17" s="1">
-        <v>1</v>
-      </c>
-      <c r="N17" s="1">
-        <v>99</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P17" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D18" s="3"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D19" s="4"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D20" s="5"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D21" s="3"/>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D22" s="5"/>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D23" s="3"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D24" s="6"/>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D25" s="5"/>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D26" s="3"/>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D27" s="3"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D28" s="3"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D29" s="6"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D30" s="3"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D31" s="4"/>
     </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="D32" s="3"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="4:4">
@@ -3226,23 +3347,9 @@
     <row r="55" s="1" customFormat="1" customHeight="1" spans="4:4">
       <c r="D55" s="4"/>
     </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="5:15">
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-      <c r="O84" s="7"/>
-    </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="5:15">
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-      <c r="O85" s="7"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3 G3 H3 F4 G4 H4 F5 G5 H5 M3:M5 O3:O5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:N5 P3:P5 C3:H5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PetTraitConfig.xlsx
+++ b/Excel/PetTraitConfig.xlsx
@@ -156,7 +156,7 @@
     <t>健壮</t>
   </si>
   <si>
-    <t>2000</t>
+    <t>3000</t>
   </si>
   <si>
     <t>基础生命</t>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="L6" s="1">
         <f t="shared" ref="L6:L19" si="0">K6*2</f>
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="M6" s="1">
         <v>2</v>

--- a/Excel/PetTraitConfig.xlsx
+++ b/Excel/PetTraitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="固定特性" sheetId="2" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="118">
   <si>
     <t>#</t>
   </si>
@@ -102,6 +102,9 @@
     <t>_ID</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
     <t>Role</t>
   </si>
   <si>
@@ -228,6 +231,18 @@
     <t>闪避</t>
   </si>
   <si>
+    <t>恢复快</t>
+  </si>
+  <si>
+    <t>恢复加成</t>
+  </si>
+  <si>
+    <t>看的准</t>
+  </si>
+  <si>
+    <t>暴击概率</t>
+  </si>
+  <si>
     <t>打的狠</t>
   </si>
   <si>
@@ -406,6 +421,33 @@
   </si>
   <si>
     <t>掉率加成+3%，品质加成+3%</t>
+  </si>
+  <si>
+    <t>战魂</t>
+  </si>
+  <si>
+    <t>1007,2007</t>
+  </si>
+  <si>
+    <t>物伤加成，物伤增幅</t>
+  </si>
+  <si>
+    <t>法魂</t>
+  </si>
+  <si>
+    <t>1008,2008</t>
+  </si>
+  <si>
+    <t>魔伤加成，魔伤增幅</t>
+  </si>
+  <si>
+    <t>道魂</t>
+  </si>
+  <si>
+    <t>1009,2009</t>
+  </si>
+  <si>
+    <t>道伤加成，道伤增幅</t>
   </si>
 </sst>
 </file>
@@ -1065,13 +1107,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -1393,31 +1435,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P105"/>
+  <dimension ref="C1:Q107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="12.8333333333333" style="1" customWidth="1"/>
-    <col min="5" max="9" width="13" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.3333333333333" style="1" customWidth="1"/>
-    <col min="12" max="13" width="11.5833333333333" style="1" customWidth="1"/>
-    <col min="14" max="15" width="9" style="1"/>
-    <col min="16" max="16" width="14.1666666666667" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="12.8333333333333" style="1" customWidth="1"/>
+    <col min="6" max="10" width="13" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="13" max="14" width="11.5833333333333" style="1" customWidth="1"/>
+    <col min="15" max="16" width="9" style="1"/>
+    <col min="17" max="17" width="14.1666666666667" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:16">
-      <c r="P1" s="1" t="s">
+    <row r="1" customHeight="1" spans="3:17">
+      <c r="Q1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="3:16">
-      <c r="P2" s="1" t="s">
+    <row r="2" customHeight="1" spans="3:17">
+      <c r="Q2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1460,10 +1502,13 @@
       <c r="P3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -1504,1038 +1549,1194 @@
       <c r="P4" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
         <v>0</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1">
+        <v>6</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>999</v>
+      </c>
+      <c r="J6" s="1">
         <v>100</v>
       </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>100</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="1">
-        <f t="shared" ref="L6:L19" si="0">K6*2</f>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="1">
+        <f t="shared" ref="M6:M19" si="0">L6*2</f>
         <v>6000</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>2</v>
       </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
       <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>999</v>
+      </c>
+      <c r="J7" s="1">
         <v>100</v>
       </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>100</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>2</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="1">
+      <c r="L7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="1">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
         <v>2</v>
       </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
       <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="F8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="1">
+        <v>6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>999</v>
+      </c>
+      <c r="J8" s="1">
         <v>100</v>
       </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>100</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>3</v>
       </c>
-      <c r="K8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="1">
+      <c r="L8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="1">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>2</v>
       </c>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
       <c r="O8" s="1">
-        <v>0</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="1">
+        <v>6</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>999</v>
+      </c>
+      <c r="J9" s="1">
         <v>100</v>
       </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>100</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>4</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L9" s="1">
+      <c r="L9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1">
         <v>2</v>
       </c>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
       <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="1">
+        <v>6</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>999</v>
+      </c>
+      <c r="J10" s="1">
         <v>100</v>
       </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>100</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>5</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="L10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="M10" s="1">
+      <c r="N10" s="1">
         <v>2</v>
       </c>
-      <c r="N10" s="1">
-        <v>0</v>
-      </c>
       <c r="O10" s="1">
-        <v>0</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="1">
+        <v>6</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>999</v>
+      </c>
+      <c r="J11" s="1">
         <v>100</v>
       </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>100</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>6</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" s="1">
+      <c r="L11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="M11" s="1">
+      <c r="N11" s="1">
         <v>2</v>
       </c>
-      <c r="N11" s="1">
+      <c r="O11" s="1">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C12" s="1">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
         <v>0</v>
       </c>
-      <c r="O11" s="1">
-        <v>0</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C12" s="1">
-        <v>10</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="1">
-        <v>100</v>
+      <c r="F12" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="J12" s="1">
         <v>10</v>
       </c>
       <c r="K12" s="1">
+        <v>10</v>
+      </c>
+      <c r="L12" s="1">
         <v>5</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M12" s="1">
-        <v>1</v>
-      </c>
       <c r="N12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C13" s="1">
         <v>11</v>
       </c>
       <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
         <v>0</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="1">
-        <v>100</v>
+      <c r="F13" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="1">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="J13" s="1">
+        <v>10</v>
+      </c>
+      <c r="K13" s="1">
         <v>11</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>5</v>
       </c>
-      <c r="L13" s="1">
+      <c r="M13" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M13" s="1">
-        <v>1</v>
-      </c>
       <c r="N13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="1">
-        <v>0</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:16">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:17">
       <c r="C14" s="1">
         <v>12</v>
       </c>
       <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="1">
-        <v>100</v>
+      <c r="F14" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="1">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="J14" s="1">
+        <v>10</v>
+      </c>
+      <c r="K14" s="1">
         <v>12</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>5</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M14" s="1">
-        <v>1</v>
-      </c>
       <c r="N14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>1</v>
+      </c>
+      <c r="P14" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C15" s="1">
         <v>13</v>
       </c>
       <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
         <v>0</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="1">
-        <v>100</v>
+      <c r="F15" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="1">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="J15" s="1">
+        <v>10</v>
+      </c>
+      <c r="K15" s="1">
         <v>13</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>5</v>
       </c>
-      <c r="L15" s="1">
+      <c r="M15" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M15" s="1">
-        <v>1</v>
-      </c>
       <c r="N15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="1">
-        <v>0</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C16" s="1">
         <v>14</v>
       </c>
       <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
         <v>0</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="1">
-        <v>100</v>
+      <c r="F16" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="G16" s="1">
+        <v>24</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1">
+        <v>999</v>
+      </c>
+      <c r="J16" s="1">
+        <v>10</v>
+      </c>
+      <c r="K16" s="1">
+        <v>14</v>
+      </c>
+      <c r="L16" s="1">
+        <v>5</v>
+      </c>
+      <c r="M16" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N16" s="1">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1">
+        <v>1</v>
+      </c>
+      <c r="P16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C17" s="1">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
         <v>0</v>
       </c>
-      <c r="H16" s="1">
+      <c r="F17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="1">
+        <v>24</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1">
+        <v>999</v>
+      </c>
+      <c r="J17" s="1">
+        <v>10</v>
+      </c>
+      <c r="K17" s="1">
+        <v>15</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5</v>
+      </c>
+      <c r="M17" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1</v>
+      </c>
+      <c r="P17" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C18" s="1">
+        <v>21</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
         <v>0</v>
       </c>
-      <c r="I16" s="1">
-        <v>100</v>
-      </c>
-      <c r="J16" s="1">
-        <v>14</v>
-      </c>
-      <c r="K16" s="1">
+      <c r="F18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="1">
+        <v>24</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <v>999</v>
+      </c>
+      <c r="J18" s="1">
+        <v>10</v>
+      </c>
+      <c r="K18" s="1">
+        <v>21</v>
+      </c>
+      <c r="L18" s="1">
         <v>5</v>
       </c>
-      <c r="L16" s="1">
+      <c r="M18" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M16" s="1">
-        <v>1</v>
-      </c>
-      <c r="N16" s="1">
+      <c r="N18" s="1">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1">
+        <v>1</v>
+      </c>
+      <c r="P18" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C19" s="1">
+        <v>22</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
         <v>0</v>
       </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C17" s="1">
+      <c r="F19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="1">
+        <v>24</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1">
+        <v>999</v>
+      </c>
+      <c r="J19" s="1">
+        <v>10</v>
+      </c>
+      <c r="K19" s="1">
         <v>22</v>
       </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="1">
-        <v>100</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1">
-        <v>100</v>
-      </c>
-      <c r="J17" s="1">
-        <v>22</v>
-      </c>
-      <c r="K17" s="1">
+      <c r="L19" s="1">
         <v>20</v>
       </c>
-      <c r="L17" s="1">
+      <c r="M19" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="M17" s="1">
-        <v>1</v>
-      </c>
-      <c r="N17" s="1">
+      <c r="N19" s="1">
+        <v>1</v>
+      </c>
+      <c r="O19" s="1">
+        <v>1</v>
+      </c>
+      <c r="P19" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C22" s="1">
+        <v>81</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
         <v>0</v>
       </c>
-      <c r="O17" s="1">
+      <c r="F22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="1">
+        <v>24</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <v>999</v>
+      </c>
+      <c r="J22" s="1">
+        <v>20</v>
+      </c>
+      <c r="K22" s="1">
+        <v>81</v>
+      </c>
+      <c r="L22" s="1">
+        <v>5</v>
+      </c>
+      <c r="M22" s="1">
+        <f t="shared" ref="M22:M27" si="1">L22*2</f>
+        <v>10</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1">
+        <v>1</v>
+      </c>
+      <c r="P22" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C23" s="1">
+        <v>82</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
         <v>0</v>
       </c>
-      <c r="P17" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C20" s="1">
-        <v>81</v>
-      </c>
-      <c r="D20" s="1">
+      <c r="F23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="1">
+        <v>24</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1">
+        <v>999</v>
+      </c>
+      <c r="J23" s="1">
+        <v>20</v>
+      </c>
+      <c r="K23" s="1">
+        <v>82</v>
+      </c>
+      <c r="L23" s="1">
+        <v>5</v>
+      </c>
+      <c r="M23" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N23" s="1">
+        <v>1</v>
+      </c>
+      <c r="O23" s="1">
+        <v>1</v>
+      </c>
+      <c r="P23" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C24" s="1">
+        <v>83</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
         <v>0</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="1">
-        <v>100</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1">
-        <v>100</v>
-      </c>
-      <c r="J20" s="1">
-        <v>81</v>
-      </c>
-      <c r="K20" s="1">
-        <v>5</v>
-      </c>
-      <c r="L20" s="1">
-        <f t="shared" ref="L20:L25" si="1">K20*2</f>
-        <v>10</v>
-      </c>
-      <c r="M20" s="1">
-        <v>1</v>
-      </c>
-      <c r="N20" s="1">
-        <v>0</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C21" s="1">
-        <v>82</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="1">
-        <v>100</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1">
-        <v>100</v>
-      </c>
-      <c r="J21" s="1">
-        <v>82</v>
-      </c>
-      <c r="K21" s="1">
-        <v>5</v>
-      </c>
-      <c r="L21" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="M21" s="1">
-        <v>1</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C22" s="1">
+      <c r="F24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24" s="1">
+        <v>24</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <v>999</v>
+      </c>
+      <c r="J24" s="1">
+        <v>20</v>
+      </c>
+      <c r="K24" s="1">
         <v>83</v>
       </c>
-      <c r="D22" s="1">
-        <v>0</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="1">
-        <v>100</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1">
-        <v>100</v>
-      </c>
-      <c r="J22" s="1">
-        <v>83</v>
-      </c>
-      <c r="K22" s="1">
+      <c r="L24" s="1">
         <v>3</v>
       </c>
-      <c r="L22" s="1">
+      <c r="M24" s="1">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M22" s="1">
-        <v>1</v>
-      </c>
-      <c r="N22" s="1">
+      <c r="N24" s="1">
+        <v>1</v>
+      </c>
+      <c r="O24" s="1">
+        <v>1</v>
+      </c>
+      <c r="P24" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C25" s="1">
+        <v>84</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
         <v>0</v>
       </c>
-      <c r="O22" s="1">
-        <v>0</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C23" s="1">
+      <c r="F25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" s="1">
+        <v>24</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1">
+        <v>999</v>
+      </c>
+      <c r="J25" s="1">
+        <v>20</v>
+      </c>
+      <c r="K25" s="1">
         <v>84</v>
       </c>
-      <c r="D23" s="1">
-        <v>0</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F23" s="1">
-        <v>100</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1">
-        <v>100</v>
-      </c>
-      <c r="J23" s="1">
-        <v>84</v>
-      </c>
-      <c r="K23" s="1">
+      <c r="L25" s="1">
         <v>3</v>
       </c>
-      <c r="L23" s="1">
+      <c r="M25" s="1">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M23" s="1">
-        <v>1</v>
-      </c>
-      <c r="N23" s="1">
+      <c r="N25" s="1">
+        <v>1</v>
+      </c>
+      <c r="O25" s="1">
+        <v>1</v>
+      </c>
+      <c r="P25" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C26" s="1">
+        <v>85</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
         <v>0</v>
       </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C24" s="1">
+      <c r="F26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="1">
+        <v>24</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
+        <v>999</v>
+      </c>
+      <c r="J26" s="1">
+        <v>20</v>
+      </c>
+      <c r="K26" s="1">
         <v>85</v>
       </c>
-      <c r="D24" s="1">
-        <v>0</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24" s="1">
-        <v>100</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1">
-        <v>100</v>
-      </c>
-      <c r="J24" s="1">
-        <v>85</v>
-      </c>
-      <c r="K24" s="1">
-        <v>10</v>
-      </c>
-      <c r="L24" s="1">
+      <c r="L26" s="1">
+        <v>10</v>
+      </c>
+      <c r="M26" s="1">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M24" s="1">
-        <v>1</v>
-      </c>
-      <c r="N24" s="1">
+      <c r="N26" s="1">
+        <v>1</v>
+      </c>
+      <c r="O26" s="1">
+        <v>1</v>
+      </c>
+      <c r="P26" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C27" s="1">
+        <v>86</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
         <v>0</v>
       </c>
-      <c r="O24" s="1">
-        <v>0</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C25" s="1">
+      <c r="F27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" s="1">
+        <v>24</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1">
+        <v>999</v>
+      </c>
+      <c r="J27" s="1">
+        <v>20</v>
+      </c>
+      <c r="K27" s="1">
         <v>86</v>
       </c>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F25" s="1">
-        <v>100</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>100</v>
-      </c>
-      <c r="J25" s="1">
-        <v>86</v>
-      </c>
-      <c r="K25" s="1">
-        <v>10</v>
-      </c>
-      <c r="L25" s="1">
+      <c r="L27" s="1">
+        <v>10</v>
+      </c>
+      <c r="M27" s="1">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M25" s="1">
-        <v>1</v>
-      </c>
-      <c r="N25" s="1">
-        <v>0</v>
-      </c>
-      <c r="O25" s="1">
-        <v>0</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" customHeight="1" spans="3:16">
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" customHeight="1" spans="3:16">
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" customHeight="1" spans="3:16">
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" customHeight="1" spans="3:16">
-      <c r="D30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="3:16">
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" customHeight="1" spans="3:16">
-      <c r="D32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="4:4">
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" customHeight="1" spans="4:4">
-      <c r="D34" s="3"/>
-    </row>
-    <row r="35" customHeight="1" spans="4:4">
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" customHeight="1" spans="4:4">
-      <c r="D36" s="3"/>
-    </row>
-    <row r="37" customHeight="1" spans="4:4">
-      <c r="D37" s="3"/>
-    </row>
-    <row r="38" customHeight="1" spans="4:4">
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" customHeight="1" spans="4:4">
-      <c r="D39" s="4"/>
-    </row>
-    <row r="40" customHeight="1" spans="4:4">
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" customHeight="1" spans="4:4">
-      <c r="D41" s="3"/>
-    </row>
-    <row r="42" customHeight="1" spans="4:4">
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" customHeight="1" spans="4:4">
-      <c r="D43" s="3"/>
-    </row>
-    <row r="44" customHeight="1" spans="4:4">
-      <c r="D44" s="6"/>
-    </row>
-    <row r="45" customHeight="1" spans="4:4">
-      <c r="D45" s="5"/>
-    </row>
-    <row r="46" customHeight="1" spans="4:4">
-      <c r="D46" s="3"/>
-    </row>
-    <row r="47" customHeight="1" spans="4:4">
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" customHeight="1" spans="4:4">
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" customHeight="1" spans="4:4">
-      <c r="D49" s="6"/>
-    </row>
-    <row r="50" customHeight="1" spans="4:4">
-      <c r="D50" s="3"/>
-    </row>
-    <row r="51" customHeight="1" spans="4:4">
-      <c r="D51" s="4"/>
-    </row>
-    <row r="52" customHeight="1" spans="4:4">
-      <c r="D52" s="3"/>
-    </row>
-    <row r="53" customHeight="1" spans="4:4">
-      <c r="D53" s="3"/>
-    </row>
-    <row r="54" customHeight="1" spans="4:4">
-      <c r="D54" s="3"/>
-    </row>
-    <row r="55" customHeight="1" spans="4:4">
-      <c r="D55" s="3"/>
-    </row>
-    <row r="56" customHeight="1" spans="4:4">
-      <c r="D56" s="3"/>
-    </row>
-    <row r="57" customHeight="1" spans="4:4">
-      <c r="D57" s="4"/>
-    </row>
-    <row r="58" customHeight="1" spans="4:4">
-      <c r="D58" s="3"/>
-    </row>
-    <row r="59" customHeight="1" spans="4:4">
-      <c r="D59" s="3"/>
-    </row>
-    <row r="60" customHeight="1" spans="4:4">
-      <c r="D60" s="3"/>
-    </row>
-    <row r="61" customHeight="1" spans="4:4">
-      <c r="D61" s="5"/>
-    </row>
-    <row r="62" customHeight="1" spans="4:4">
-      <c r="D62" s="3"/>
-    </row>
-    <row r="63" customHeight="1" spans="4:4">
-      <c r="D63" s="4"/>
-    </row>
-    <row r="64" customHeight="1" spans="4:4">
-      <c r="D64" s="3"/>
-    </row>
-    <row r="65" customHeight="1" spans="4:4">
-      <c r="D65" s="6"/>
-    </row>
-    <row r="66" customHeight="1" spans="4:4">
-      <c r="D66" s="3"/>
-    </row>
-    <row r="67" customHeight="1" spans="4:4">
-      <c r="D67" s="3"/>
-    </row>
-    <row r="68" customHeight="1" spans="4:4">
-      <c r="D68" s="3"/>
-    </row>
-    <row r="69" customHeight="1" spans="4:4">
-      <c r="D69" s="4"/>
-    </row>
-    <row r="70" customHeight="1" spans="4:4">
-      <c r="D70" s="3"/>
-    </row>
-    <row r="71" customHeight="1" spans="4:4">
-      <c r="D71" s="3"/>
-    </row>
-    <row r="72" customHeight="1" spans="4:4">
-      <c r="D72" s="3"/>
-    </row>
-    <row r="73" customHeight="1" spans="4:4">
-      <c r="D73" s="3"/>
-    </row>
-    <row r="74" customHeight="1" spans="4:4">
-      <c r="D74" s="5"/>
-    </row>
-    <row r="75" customHeight="1" spans="4:4">
-      <c r="D75" s="4"/>
-    </row>
-    <row r="84" customHeight="1" spans="7:8">
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-    </row>
-    <row r="85" customHeight="1" spans="7:8">
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-    </row>
-    <row r="104" customHeight="1" spans="5:16">
-      <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
-      <c r="P104" s="7"/>
-    </row>
-    <row r="105" customHeight="1" spans="5:16">
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="P105" s="7"/>
+      <c r="N27" s="1">
+        <v>1</v>
+      </c>
+      <c r="O27" s="1">
+        <v>1</v>
+      </c>
+      <c r="P27" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" customHeight="1" spans="3:17">
+      <c r="E29" s="6"/>
+    </row>
+    <row r="30" customHeight="1" spans="3:17">
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:17">
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" customHeight="1" spans="3:17">
+      <c r="E32" s="5"/>
+    </row>
+    <row r="33" customHeight="1" spans="5:5">
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" customHeight="1" spans="5:5">
+      <c r="E34" s="5"/>
+    </row>
+    <row r="35" customHeight="1" spans="5:5">
+      <c r="E35" s="6"/>
+    </row>
+    <row r="36" customHeight="1" spans="5:5">
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" customHeight="1" spans="5:5">
+      <c r="E37" s="3"/>
+    </row>
+    <row r="38" customHeight="1" spans="5:5">
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" customHeight="1" spans="5:5">
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" customHeight="1" spans="5:5">
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" customHeight="1" spans="5:5">
+      <c r="E41" s="6"/>
+    </row>
+    <row r="42" customHeight="1" spans="5:5">
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" customHeight="1" spans="5:5">
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" customHeight="1" spans="5:5">
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" customHeight="1" spans="5:5">
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" customHeight="1" spans="5:5">
+      <c r="E46" s="5"/>
+    </row>
+    <row r="47" customHeight="1" spans="5:5">
+      <c r="E47" s="4"/>
+    </row>
+    <row r="48" customHeight="1" spans="5:5">
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" customHeight="1" spans="5:5">
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" customHeight="1" spans="5:5">
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" customHeight="1" spans="5:5">
+      <c r="E51" s="5"/>
+    </row>
+    <row r="52" customHeight="1" spans="5:5">
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" customHeight="1" spans="5:5">
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" customHeight="1" spans="5:5">
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" customHeight="1" spans="5:5">
+      <c r="E55" s="3"/>
+    </row>
+    <row r="56" customHeight="1" spans="5:5">
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" customHeight="1" spans="5:5">
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" customHeight="1" spans="5:5">
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" customHeight="1" spans="5:5">
+      <c r="E59" s="6"/>
+    </row>
+    <row r="60" customHeight="1" spans="5:5">
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" customHeight="1" spans="5:5">
+      <c r="E61" s="3"/>
+    </row>
+    <row r="62" customHeight="1" spans="5:5">
+      <c r="E62" s="3"/>
+    </row>
+    <row r="63" customHeight="1" spans="5:5">
+      <c r="E63" s="4"/>
+    </row>
+    <row r="64" customHeight="1" spans="5:5">
+      <c r="E64" s="3"/>
+    </row>
+    <row r="65" customHeight="1" spans="5:5">
+      <c r="E65" s="6"/>
+    </row>
+    <row r="66" customHeight="1" spans="5:5">
+      <c r="E66" s="3"/>
+    </row>
+    <row r="67" customHeight="1" spans="5:5">
+      <c r="E67" s="5"/>
+    </row>
+    <row r="68" customHeight="1" spans="5:5">
+      <c r="E68" s="3"/>
+    </row>
+    <row r="69" customHeight="1" spans="5:5">
+      <c r="E69" s="3"/>
+    </row>
+    <row r="70" customHeight="1" spans="5:5">
+      <c r="E70" s="3"/>
+    </row>
+    <row r="71" customHeight="1" spans="5:5">
+      <c r="E71" s="6"/>
+    </row>
+    <row r="72" customHeight="1" spans="5:5">
+      <c r="E72" s="3"/>
+    </row>
+    <row r="73" customHeight="1" spans="5:5">
+      <c r="E73" s="3"/>
+    </row>
+    <row r="74" customHeight="1" spans="5:5">
+      <c r="E74" s="3"/>
+    </row>
+    <row r="75" customHeight="1" spans="5:5">
+      <c r="E75" s="3"/>
+    </row>
+    <row r="76" customHeight="1" spans="5:5">
+      <c r="E76" s="4"/>
+    </row>
+    <row r="77" customHeight="1" spans="5:5">
+      <c r="E77" s="6"/>
+    </row>
+    <row r="86" customHeight="1" spans="8:9">
+      <c r="H86" s="7"/>
+      <c r="I86" s="7"/>
+    </row>
+    <row r="87" customHeight="1" spans="8:9">
+      <c r="H87" s="7"/>
+      <c r="I87" s="7"/>
+    </row>
+    <row r="106" customHeight="1" spans="6:17">
+      <c r="F106" s="7"/>
+      <c r="G106" s="7"/>
+      <c r="Q106" s="7"/>
+    </row>
+    <row r="107" customHeight="1" spans="6:17">
+      <c r="F107" s="7"/>
+      <c r="G107" s="7"/>
+      <c r="Q107" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:N5 P3:P5 C3:H5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 D4 D5 C3:C5 O3:O5 Q3:Q5 E3:I5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2548,32 +2749,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P55"/>
+  <dimension ref="C1:Q55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="12.8333333333333" style="1" customWidth="1"/>
-    <col min="5" max="9" width="13" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.1666666666667" style="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="13" max="14" width="13.8333333333333" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9" style="1"/>
-    <col min="16" max="16" width="23.5833333333333" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="12.8333333333333" style="1" customWidth="1"/>
+    <col min="6" max="10" width="13" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1666666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="14" max="15" width="13.8333333333333" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9" style="1"/>
+    <col min="17" max="17" width="23.5833333333333" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:16">
-      <c r="P1" s="1" t="s">
+    <row r="1" customHeight="1" spans="3:17">
+      <c r="Q1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="3:16">
-      <c r="P2" s="1" t="s">
+    <row r="2" customHeight="1" spans="3:17">
+      <c r="Q2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2616,10 +2817,13 @@
       <c r="P3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -2660,696 +2864,870 @@
       <c r="P4" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
       <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1">
         <v>0</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="F6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="1">
         <v>6</v>
       </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
       <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
         <v>999</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>100</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="K6" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N6" s="1">
-        <v>1</v>
+        <v>66</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1">
         <v>99</v>
       </c>
-      <c r="P6" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q6" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
       <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="F7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="1">
         <v>6</v>
       </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
       <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
         <v>999</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>100</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="K7" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="M7" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N7" s="1">
-        <v>1</v>
+        <v>66</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="O7" s="1">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1">
         <v>99</v>
       </c>
-      <c r="P7" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q7" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
       <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="1">
+        <v>6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>999</v>
+      </c>
+      <c r="J8" s="1">
+        <v>100</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="1">
-        <v>6</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
-        <v>999</v>
-      </c>
-      <c r="I8" s="1">
-        <v>100</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N8" s="1">
-        <v>1</v>
-      </c>
       <c r="O8" s="1">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1">
         <v>99</v>
       </c>
-      <c r="P8" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q8" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
       <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="F9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="1">
         <v>48</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>19</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>999</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>30</v>
       </c>
-      <c r="J9" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="K9" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N9" s="1">
+        <v>78</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O9" s="1">
         <v>5</v>
       </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
         <v>99</v>
       </c>
-      <c r="P9" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q9" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
       <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="F10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="1">
         <v>48</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>19</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>999</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>30</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="K10" s="8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N10" s="1">
+        <v>83</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O10" s="1">
         <v>5</v>
       </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
         <v>99</v>
       </c>
-      <c r="P10" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q10" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
       <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="F11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="1">
         <v>36</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>13</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>999</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>30</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="K11" s="8" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N11" s="1">
+        <v>78</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O11" s="1">
         <v>5</v>
       </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
         <v>99</v>
       </c>
-      <c r="P11" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q11" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
       <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
         <v>0</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="F12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" s="1">
         <v>24</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>13</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>999</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>50</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>84</v>
-      </c>
       <c r="K12" s="8" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N12" s="1">
+        <v>90</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O12" s="1">
         <v>4</v>
       </c>
-      <c r="O12" s="1">
+      <c r="P12" s="1">
         <v>99</v>
       </c>
-      <c r="P12" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q12" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
       <c r="D13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1">
         <v>0</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="1">
+      <c r="F13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="1">
         <v>24</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>13</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>999</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>50</v>
       </c>
-      <c r="J13" s="8" t="s">
-        <v>88</v>
-      </c>
       <c r="K13" s="8" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N13" s="1">
+        <v>90</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O13" s="1">
         <v>4</v>
       </c>
-      <c r="O13" s="1">
+      <c r="P13" s="1">
         <v>99</v>
       </c>
-      <c r="P13" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q13" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
       <c r="D14" s="1">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="1">
+        <v>24</v>
+      </c>
+      <c r="H14" s="1">
+        <v>13</v>
+      </c>
+      <c r="I14" s="1">
+        <v>999</v>
+      </c>
+      <c r="J14" s="1">
+        <v>25</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="M14" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="1">
-        <v>24</v>
-      </c>
-      <c r="G14" s="1">
-        <v>13</v>
-      </c>
-      <c r="H14" s="1">
-        <v>999</v>
-      </c>
-      <c r="I14" s="1">
-        <v>25</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N14" s="1">
+      <c r="N14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O14" s="1">
         <v>4</v>
       </c>
-      <c r="O14" s="1">
+      <c r="P14" s="1">
         <v>99</v>
       </c>
-      <c r="P14" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q14" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
       <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
         <v>0</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="F15" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="1">
         <v>24</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>7</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>999</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <v>50</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>94</v>
-      </c>
       <c r="K15" s="8" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N15" s="1">
-        <v>1</v>
+        <v>90</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="O15" s="1">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1">
         <v>99</v>
       </c>
-      <c r="P15" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q15" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
       <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1">
         <v>0</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" s="1">
+      <c r="F16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="1">
         <v>24</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>7</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>999</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>50</v>
       </c>
-      <c r="J16" s="8" t="s">
-        <v>97</v>
-      </c>
       <c r="K16" s="8" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N16" s="1">
-        <v>1</v>
+        <v>90</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="O16" s="1">
+        <v>1</v>
+      </c>
+      <c r="P16" s="1">
         <v>99</v>
       </c>
-      <c r="P16" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q16" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C17" s="1">
         <v>1012</v>
       </c>
       <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
         <v>0</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" s="1">
+        <v>24</v>
+      </c>
+      <c r="H17" s="1">
+        <v>7</v>
+      </c>
+      <c r="I17" s="1">
+        <v>999</v>
+      </c>
+      <c r="J17" s="1">
+        <v>10</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1</v>
+      </c>
+      <c r="P17" s="1">
         <v>99</v>
       </c>
-      <c r="F17" s="1">
-        <v>24</v>
-      </c>
-      <c r="G17" s="1">
+      <c r="Q17" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="16" customHeight="1" spans="3:17">
+      <c r="C18" s="1">
+        <v>1013</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="1">
+        <v>6</v>
+      </c>
+      <c r="H18" s="1">
         <v>7</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I18" s="1">
         <v>999</v>
       </c>
-      <c r="I17" s="1">
-        <v>10</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="J18" s="1">
         <v>100</v>
       </c>
-      <c r="K17" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N17" s="1">
-        <v>1</v>
-      </c>
-      <c r="O17" s="1">
+      <c r="K18" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O18" s="1">
+        <v>4</v>
+      </c>
+      <c r="P18" s="1">
         <v>99</v>
       </c>
-      <c r="P17" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D24" s="6"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D29" s="6"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D34" s="3"/>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D36" s="3"/>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D37" s="4"/>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D40" s="3"/>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D42" s="3"/>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D43" s="4"/>
-    </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D44" s="3"/>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D45" s="6"/>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D46" s="3"/>
-    </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D49" s="4"/>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D50" s="3"/>
-    </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D51" s="3"/>
-    </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D52" s="3"/>
-    </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D53" s="3"/>
-    </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D54" s="5"/>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D55" s="4"/>
+      <c r="Q18" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="16" customHeight="1" spans="3:17">
+      <c r="C19" s="1">
+        <v>1014</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G19" s="1">
+        <v>6</v>
+      </c>
+      <c r="H19" s="1">
+        <v>7</v>
+      </c>
+      <c r="I19" s="1">
+        <v>999</v>
+      </c>
+      <c r="J19" s="1">
+        <v>100</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O19" s="1">
+        <v>4</v>
+      </c>
+      <c r="P19" s="1">
+        <v>99</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="16" customHeight="1" spans="3:17">
+      <c r="C20" s="1">
+        <v>1015</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G20" s="1">
+        <v>6</v>
+      </c>
+      <c r="H20" s="1">
+        <v>7</v>
+      </c>
+      <c r="I20" s="1">
+        <v>999</v>
+      </c>
+      <c r="J20" s="1">
+        <v>100</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O20" s="1">
+        <v>4</v>
+      </c>
+      <c r="P20" s="1">
+        <v>99</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E31" s="6"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E37" s="6"/>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E43" s="6"/>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E45" s="5"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E54" s="4"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="E55" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:N5 P3:P5 C3:H5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 D4 D5 C3:C5 O3:O5 Q3:Q5 E3:I5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PetTraitConfig.xlsx
+++ b/Excel/PetTraitConfig.xlsx
@@ -225,7 +225,7 @@
     <t>命中</t>
   </si>
   <si>
-    <t>躲得准</t>
+    <t>躲得快</t>
   </si>
   <si>
     <t>闪避</t>
@@ -237,7 +237,7 @@
     <t>恢复加成</t>
   </si>
   <si>
-    <t>看的准</t>
+    <t>瞅的准</t>
   </si>
   <si>
     <t>暴击概率</t>
@@ -1927,7 +1927,7 @@
         <v>1</v>
       </c>
       <c r="O12" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P12" s="1">
         <v>10</v>
@@ -1975,7 +1975,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P13" s="1">
         <v>10</v>
@@ -2023,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P14" s="1">
         <v>10</v>
@@ -2071,7 +2071,7 @@
         <v>1</v>
       </c>
       <c r="O15" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P15" s="1">
         <v>10</v>
@@ -2119,7 +2119,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P16" s="1">
         <v>10</v>
@@ -2167,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P17" s="1">
         <v>10</v>
@@ -2215,7 +2215,7 @@
         <v>1</v>
       </c>
       <c r="O18" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P18" s="1">
         <v>10</v>
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="O19" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P19" s="1">
         <v>10</v>
@@ -2317,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P22" s="1">
         <v>10</v>
@@ -2365,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="O23" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P23" s="1">
         <v>10</v>
@@ -2413,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="O24" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P24" s="1">
         <v>10</v>
@@ -2461,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="O25" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P25" s="1">
         <v>10</v>
@@ -2509,7 +2509,7 @@
         <v>1</v>
       </c>
       <c r="O26" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P26" s="1">
         <v>10</v>
@@ -2557,7 +2557,7 @@
         <v>1</v>
       </c>
       <c r="O27" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P27" s="1">
         <v>10</v>
@@ -2736,7 +2736,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 D4 D5 C3:C5 O3:O5 Q3:Q5 E3:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3:O5 Q3:Q5 C3:I5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -3727,7 +3727,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 D4 D5 C3:C5 O3:O5 Q3:Q5 E3:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3:O5 Q3:Q5 C3:I5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PetTraitConfig.xlsx
+++ b/Excel/PetTraitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="固定特性" sheetId="2" r:id="rId1"/>

--- a/Excel/PetTraitConfig.xlsx
+++ b/Excel/PetTraitConfig.xlsx
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="120">
   <si>
     <t>#</t>
   </si>
@@ -327,37 +327,43 @@
     <t>11,12</t>
   </si>
   <si>
+    <t>5,10</t>
+  </si>
+  <si>
+    <t>10,20</t>
+  </si>
+  <si>
+    <t>攻击速度+5%，移动速度+10%</t>
+  </si>
+  <si>
+    <t>子弹时间</t>
+  </si>
+  <si>
+    <t>10,22</t>
+  </si>
+  <si>
+    <t>5,25</t>
+  </si>
+  <si>
+    <t>10,50</t>
+  </si>
+  <si>
+    <t>技能冷却+5%，暴击伤害+25%</t>
+  </si>
+  <si>
+    <t>射手直觉</t>
+  </si>
+  <si>
+    <t>13,14</t>
+  </si>
+  <si>
     <t>5,5</t>
   </si>
   <si>
     <t>10,10</t>
   </si>
   <si>
-    <t>攻击速度+10%，移动速度+10%</t>
-  </si>
-  <si>
-    <t>子弹时间</t>
-  </si>
-  <si>
-    <t>10,22</t>
-  </si>
-  <si>
-    <t>5,25</t>
-  </si>
-  <si>
-    <t>10,50</t>
-  </si>
-  <si>
-    <t>技能冷却+10%，暴击伤害+50%</t>
-  </si>
-  <si>
-    <t>射手直觉</t>
-  </si>
-  <si>
-    <t>13,14</t>
-  </si>
-  <si>
-    <t>命中+10%，闪避+10%</t>
+    <t>命中+5%，闪避+5%</t>
   </si>
   <si>
     <t>真男人</t>
@@ -1911,7 +1917,7 @@
         <v>999</v>
       </c>
       <c r="J12" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K12" s="1">
         <v>10</v>
@@ -1959,7 +1965,7 @@
         <v>999</v>
       </c>
       <c r="J13" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K13" s="1">
         <v>11</v>
@@ -2007,17 +2013,17 @@
         <v>999</v>
       </c>
       <c r="J14" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="K14" s="1">
         <v>12</v>
       </c>
       <c r="L14" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M14" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N14" s="1">
         <v>1</v>
@@ -2055,7 +2061,7 @@
         <v>999</v>
       </c>
       <c r="J15" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K15" s="1">
         <v>13</v>
@@ -2103,7 +2109,7 @@
         <v>999</v>
       </c>
       <c r="J16" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K16" s="1">
         <v>14</v>
@@ -2151,7 +2157,7 @@
         <v>999</v>
       </c>
       <c r="J17" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K17" s="1">
         <v>15</v>
@@ -2247,7 +2253,7 @@
         <v>999</v>
       </c>
       <c r="J19" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K19" s="1">
         <v>22</v>
@@ -2929,7 +2935,7 @@
         <v>63</v>
       </c>
       <c r="G6" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -2976,7 +2982,7 @@
         <v>69</v>
       </c>
       <c r="G7" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -3023,7 +3029,7 @@
         <v>72</v>
       </c>
       <c r="G8" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -3070,7 +3076,7 @@
         <v>75</v>
       </c>
       <c r="G9" s="1">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H9" s="1">
         <v>19</v>
@@ -3079,7 +3085,7 @@
         <v>999</v>
       </c>
       <c r="J9" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>76</v>
@@ -3117,7 +3123,7 @@
         <v>80</v>
       </c>
       <c r="G10" s="1">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H10" s="1">
         <v>19</v>
@@ -3126,7 +3132,7 @@
         <v>999</v>
       </c>
       <c r="J10" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>81</v>
@@ -3164,7 +3170,7 @@
         <v>85</v>
       </c>
       <c r="G11" s="1">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H11" s="1">
         <v>13</v>
@@ -3179,10 +3185,10 @@
         <v>86</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>67</v>
@@ -3194,7 +3200,7 @@
         <v>99</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3208,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G12" s="1">
         <v>24</v>
@@ -3223,13 +3229,13 @@
         <v>50</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>67</v>
@@ -3241,7 +3247,7 @@
         <v>99</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3255,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G13" s="1">
         <v>24</v>
@@ -3270,13 +3276,13 @@
         <v>50</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N13" s="8" t="s">
         <v>67</v>
@@ -3288,7 +3294,7 @@
         <v>99</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3302,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G14" s="1">
         <v>24</v>
@@ -3317,13 +3323,13 @@
         <v>25</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N14" s="8" t="s">
         <v>67</v>
@@ -3335,7 +3341,7 @@
         <v>99</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3349,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G15" s="1">
         <v>24</v>
@@ -3364,13 +3370,13 @@
         <v>50</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N15" s="8" t="s">
         <v>67</v>
@@ -3382,7 +3388,7 @@
         <v>99</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3396,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G16" s="1">
         <v>24</v>
@@ -3411,13 +3417,13 @@
         <v>50</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N16" s="8" t="s">
         <v>67</v>
@@ -3429,7 +3435,7 @@
         <v>99</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3443,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G17" s="1">
         <v>24</v>
@@ -3458,13 +3464,13 @@
         <v>10</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N17" s="8" t="s">
         <v>67</v>
@@ -3476,7 +3482,7 @@
         <v>99</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="16" customHeight="1" spans="3:17">
@@ -3490,10 +3496,10 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G18" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H18" s="1">
         <v>7</v>
@@ -3505,7 +3511,7 @@
         <v>100</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>65</v>
@@ -3523,7 +3529,7 @@
         <v>99</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="16" customHeight="1" spans="3:17">
@@ -3537,10 +3543,10 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G19" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H19" s="1">
         <v>7</v>
@@ -3552,7 +3558,7 @@
         <v>100</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>65</v>
@@ -3570,7 +3576,7 @@
         <v>99</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="16" customHeight="1" spans="3:17">
@@ -3584,10 +3590,10 @@
         <v>3</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G20" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H20" s="1">
         <v>7</v>
@@ -3599,7 +3605,7 @@
         <v>100</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>65</v>
@@ -3617,7 +3623,7 @@
         <v>99</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
